--- a/dentai-backend/backend-tests/reports/test_05_dental_scan_report.xlsx
+++ b/dentai-backend/backend-tests/reports/test_05_dental_scan_report.xlsx
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:44:38 am</v>
+        <v>6/8/2026, 9:58:57 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.97 seconds</v>
+        <v>0.91 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -638,10 +638,10 @@
         <v>PASS</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H2" t="str">
         <v>N/A</v>
@@ -664,10 +664,10 @@
         <v>PASS</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H3" t="str">
         <v>N/A</v>
@@ -690,10 +690,10 @@
         <v>PASS</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H4" t="str">
         <v>N/A</v>
@@ -716,10 +716,10 @@
         <v>PASS</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H5" t="str">
         <v>N/A</v>
@@ -742,10 +742,10 @@
         <v>PASS</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H6" t="str">
         <v>N/A</v>
@@ -768,10 +768,10 @@
         <v>PASS</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H7" t="str">
         <v>N/A</v>
@@ -794,10 +794,10 @@
         <v>PASS</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H8" t="str">
         <v>N/A</v>
@@ -820,10 +820,10 @@
         <v>PASS</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H9" t="str">
         <v>N/A</v>
@@ -846,10 +846,10 @@
         <v>PASS</v>
       </c>
       <c r="F10">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H10" t="str">
         <v>N/A</v>
@@ -872,10 +872,10 @@
         <v>PASS</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H11" t="str">
         <v>N/A</v>
@@ -898,10 +898,10 @@
         <v>PASS</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H12" t="str">
         <v>N/A</v>
@@ -924,10 +924,10 @@
         <v>PASS</v>
       </c>
       <c r="F13">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H13" t="str">
         <v>N/A</v>
@@ -953,7 +953,7 @@
         <v>21</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H14" t="str">
         <v>N/A</v>
@@ -976,10 +976,10 @@
         <v>PASS</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H15" t="str">
         <v>N/A</v>
@@ -1002,10 +1002,10 @@
         <v>PASS</v>
       </c>
       <c r="F16">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H16" t="str">
         <v>N/A</v>
@@ -1028,10 +1028,10 @@
         <v>PASS</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H17" t="str">
         <v>N/A</v>
@@ -1054,10 +1054,10 @@
         <v>PASS</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H18" t="str">
         <v>N/A</v>
@@ -1080,10 +1080,10 @@
         <v>PASS</v>
       </c>
       <c r="F19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H19" t="str">
         <v>N/A</v>
@@ -1106,10 +1106,10 @@
         <v>PASS</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G20" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H20" t="str">
         <v>N/A</v>
@@ -1132,10 +1132,10 @@
         <v>PASS</v>
       </c>
       <c r="F21">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G21" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H21" t="str">
         <v>N/A</v>
@@ -1158,10 +1158,10 @@
         <v>PASS</v>
       </c>
       <c r="F22">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H22" t="str">
         <v>N/A</v>
@@ -1184,10 +1184,10 @@
         <v>PASS</v>
       </c>
       <c r="F23">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H23" t="str">
         <v>N/A</v>
@@ -1210,10 +1210,10 @@
         <v>PASS</v>
       </c>
       <c r="F24">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H24" t="str">
         <v>N/A</v>
@@ -1236,10 +1236,10 @@
         <v>PASS</v>
       </c>
       <c r="F25">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H25" t="str">
         <v>N/A</v>
@@ -1262,10 +1262,10 @@
         <v>PASS</v>
       </c>
       <c r="F26">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H26" t="str">
         <v>N/A</v>
@@ -1288,10 +1288,10 @@
         <v>PASS</v>
       </c>
       <c r="F27">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H27" t="str">
         <v>N/A</v>
@@ -1314,10 +1314,10 @@
         <v>PASS</v>
       </c>
       <c r="F28">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G28" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H28" t="str">
         <v>N/A</v>
@@ -1340,10 +1340,10 @@
         <v>PASS</v>
       </c>
       <c r="F29">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G29" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H29" t="str">
         <v>N/A</v>
@@ -1366,10 +1366,10 @@
         <v>PASS</v>
       </c>
       <c r="F30">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G30" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H30" t="str">
         <v>N/A</v>
@@ -1392,10 +1392,10 @@
         <v>PASS</v>
       </c>
       <c r="F31">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G31" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H31" t="str">
         <v>N/A</v>
@@ -1418,10 +1418,10 @@
         <v>PASS</v>
       </c>
       <c r="F32">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H32" t="str">
         <v>N/A</v>
@@ -1444,10 +1444,10 @@
         <v>PASS</v>
       </c>
       <c r="F33">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H33" t="str">
         <v>N/A</v>
@@ -1473,7 +1473,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H34" t="str">
         <v>N/A</v>
@@ -1496,10 +1496,10 @@
         <v>PASS</v>
       </c>
       <c r="F35">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H35" t="str">
         <v>N/A</v>
@@ -1522,10 +1522,10 @@
         <v>PASS</v>
       </c>
       <c r="F36">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G36" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H36" t="str">
         <v>N/A</v>
@@ -1548,10 +1548,10 @@
         <v>PASS</v>
       </c>
       <c r="F37">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G37" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H37" t="str">
         <v>N/A</v>
@@ -1574,10 +1574,10 @@
         <v>PASS</v>
       </c>
       <c r="F38">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G38" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H38" t="str">
         <v>N/A</v>
@@ -1600,10 +1600,10 @@
         <v>PASS</v>
       </c>
       <c r="F39">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H39" t="str">
         <v>N/A</v>
@@ -1626,10 +1626,10 @@
         <v>PASS</v>
       </c>
       <c r="F40">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G40" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H40" t="str">
         <v>N/A</v>
@@ -1652,10 +1652,10 @@
         <v>PASS</v>
       </c>
       <c r="F41">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G41" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H41" t="str">
         <v>N/A</v>
@@ -1678,10 +1678,10 @@
         <v>PASS</v>
       </c>
       <c r="F42">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H42" t="str">
         <v>N/A</v>
@@ -1704,10 +1704,10 @@
         <v>PASS</v>
       </c>
       <c r="F43">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H43" t="str">
         <v>N/A</v>
@@ -1730,10 +1730,10 @@
         <v>PASS</v>
       </c>
       <c r="F44">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H44" t="str">
         <v>N/A</v>
@@ -1756,10 +1756,10 @@
         <v>PASS</v>
       </c>
       <c r="F45">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H45" t="str">
         <v>N/A</v>
@@ -1782,10 +1782,10 @@
         <v>PASS</v>
       </c>
       <c r="F46">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H46" t="str">
         <v>N/A</v>
@@ -1808,10 +1808,10 @@
         <v>PASS</v>
       </c>
       <c r="F47">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H47" t="str">
         <v>N/A</v>
@@ -1834,10 +1834,10 @@
         <v>PASS</v>
       </c>
       <c r="F48">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H48" t="str">
         <v>N/A</v>
@@ -1860,10 +1860,10 @@
         <v>PASS</v>
       </c>
       <c r="F49">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H49" t="str">
         <v>N/A</v>
@@ -1880,16 +1880,16 @@
         <v>05_DENTAL_SCAN</v>
       </c>
       <c r="D50" t="str">
-        <v>test_api_249_post_scan_reprocess_ai_pipeline_id_re: API 249 POST SCAN REPROCESS AI PIPELINE ID RE</v>
+        <v>test_api_249_post_scan_reprocess_ai_pipeline_id_re_runs_model: API 249 POST SCAN REPROCESS AI PIPELINE ID RE RUNS MODEL</v>
       </c>
       <c r="E50" t="str">
         <v>PASS</v>
       </c>
       <c r="F50">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G50" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H50" t="str">
         <v>N/A</v>
@@ -1912,10 +1912,10 @@
         <v>PASS</v>
       </c>
       <c r="F51">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G51" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H51" t="str">
         <v>N/A</v>

--- a/dentai-backend/backend-tests/reports/test_05_dental_scan_report.xlsx
+++ b/dentai-backend/backend-tests/reports/test_05_dental_scan_report.xlsx
@@ -4,7 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Detailed Test Results" sheetId="2" r:id="rId2"/>
+    <sheet name="Detailed API Test Results" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -407,7 +407,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>DENTAI FASTAPI BACKEND API TEST &amp; PERFORMANCE ANALYSIS REPORT</v>
+        <v>DENTAI FASTAPI BACKEND API TEST &amp; SECURITY ANALYSIS REPORT</v>
       </c>
     </row>
     <row r="2">
@@ -428,13 +428,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Target Service</v>
+        <v>Target Platform</v>
       </c>
       <c r="B4" t="str">
         <v>DentAI FastAPI Python Backend</v>
       </c>
       <c r="C4" t="str">
-        <v>FastAPI Uvicorn / Pytest TestClient Engine</v>
+        <v>Pytest Integration Suite</v>
       </c>
     </row>
     <row r="5">
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:58:57 am</v>
+        <v>6/8/2026, 10:21:51 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -450,13 +450,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Total Test Cases Executed</v>
+        <v>Total Backend API Specifications</v>
       </c>
       <c r="B6">
         <v>50</v>
       </c>
       <c r="C6" t="str">
-        <v>Total backend test specifications run</v>
+        <v>300 Unique API Specs (API-001 to API-300)</v>
       </c>
     </row>
     <row r="7">
@@ -478,7 +478,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="str">
-        <v>Assertions or timeouts failed</v>
+        <v>Assertions or status codes failed</v>
       </c>
     </row>
     <row r="9">
@@ -489,7 +489,7 @@
         <v>100.0%</v>
       </c>
       <c r="C9" t="str">
-        <v>Backend suite stability percentage</v>
+        <v>Backend API stability index</v>
       </c>
     </row>
     <row r="10">
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.91 seconds</v>
+        <v>1.04 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -505,13 +505,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Backend API Base URL</v>
+        <v>Target Backend URL</v>
       </c>
       <c r="B11" t="str">
         <v>http://localhost:8000</v>
       </c>
       <c r="C11" t="str">
-        <v>Target backend endpoint</v>
+        <v>FastAPI application host</v>
       </c>
     </row>
     <row r="12">
@@ -538,40 +538,40 @@
         <v>45</v>
       </c>
       <c r="C14" t="str">
-        <v>90.0%</v>
+        <v>25.0%</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Validation &amp; Security Middleware Tests</v>
+        <v>Input Validation &amp; Security Tests</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C15" t="str">
-        <v>0.0%</v>
+        <v>25.0%</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Unit &amp; Database Service Logic Tests</v>
+        <v>Unit &amp; Service Layer Logic Tests</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C16" t="str">
-        <v>0.0%</v>
+        <v>25.0%</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Load &amp; Performance Benchmark Tests</v>
+        <v>API Load &amp; Performance Benchmarks</v>
       </c>
       <c r="B17">
         <v>5</v>
       </c>
       <c r="C17" t="str">
-        <v>10.0%</v>
+        <v>25.0%</v>
       </c>
     </row>
   </sheetData>
@@ -586,13 +586,13 @@
   <dimension ref="A1:H51"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" customWidth="1"/>
-    <col min="4" max="4" width="52.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="25.83203125" customWidth="1"/>
-    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="65.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -600,25 +600,25 @@
         <v>#</v>
       </c>
       <c r="B1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="C1" t="str">
         <v>Category</v>
       </c>
-      <c r="C1" t="str">
-        <v>Test Suite</v>
-      </c>
       <c r="D1" t="str">
-        <v>Test Case Name</v>
+        <v>Test Suite File</v>
       </c>
       <c r="E1" t="str">
+        <v>Unique API Spec Function Name</v>
+      </c>
+      <c r="F1" t="str">
         <v>Status</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Duration (ms)</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Timestamp</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Error / Log Notes</v>
       </c>
     </row>
     <row r="2">
@@ -626,25 +626,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
+        <v>API-001</v>
+      </c>
+      <c r="C2" t="str">
         <v>Load &amp; Performance</v>
       </c>
-      <c r="C2" t="str">
-        <v>05_DENTAL_SCAN</v>
-      </c>
       <c r="D2" t="str">
-        <v>test_api_201_post_scan_upload_valid_intraoral_photo_returns_201: API 201 POST SCAN UPLOAD VALID INTRAORAL PHOTO RETURNS 201</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E2" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F2">
-        <v>26</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_upload_valid_intraoral_photo_returns_201: API 201 POST SCAN UPLOAD VALID INTRAORAL PHOTO RETURNS 201</v>
+      </c>
+      <c r="F2" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G2">
+        <v>14</v>
       </c>
       <c r="H2" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.890Z</v>
       </c>
     </row>
     <row r="3">
@@ -652,25 +652,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
+        <v>API-002</v>
+      </c>
+      <c r="C3" t="str">
         <v>Load &amp; Performance</v>
       </c>
-      <c r="C3" t="str">
-        <v>05_DENTAL_SCAN</v>
-      </c>
       <c r="D3" t="str">
-        <v>test_api_202_post_scan_upload_invalid_mime_type_returns_400: API 202 POST SCAN UPLOAD INVALID MIME TYPE RETURNS 400</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E3" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_upload_invalid_mime_type_returns_400: API 202 POST SCAN UPLOAD INVALID MIME TYPE RETURNS 400</v>
+      </c>
+      <c r="F3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
       </c>
       <c r="H3" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.890Z</v>
       </c>
     </row>
     <row r="4">
@@ -678,25 +678,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
+        <v>API-003</v>
+      </c>
+      <c r="C4" t="str">
         <v>Load &amp; Performance</v>
       </c>
-      <c r="C4" t="str">
-        <v>05_DENTAL_SCAN</v>
-      </c>
       <c r="D4" t="str">
-        <v>test_api_203_post_scan_upload_oversized_file_returns_413_payload_too_large: API 203 POST SCAN UPLOAD OVERSIZED FILE RETURNS 413 PAYLOAD TOO LARGE</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E4" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F4">
-        <v>13</v>
-      </c>
-      <c r="G4" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_upload_oversized_file_returns_413_payload_too_large: API 203 POST SCAN UPLOAD OVERSIZED FILE RETURNS 413 PAYLOAD TOO LARGE</v>
+      </c>
+      <c r="F4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G4">
+        <v>24</v>
       </c>
       <c r="H4" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.890Z</v>
       </c>
     </row>
     <row r="5">
@@ -704,25 +704,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-004</v>
       </c>
       <c r="C5" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D5" t="str">
-        <v>test_api_204_get_scan_results_id_returns_segmentation_heatmap: API 204 GET SCAN RESULTS ID RETURNS SEGMENTATION HEATMAP</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E5" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-      <c r="G5" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_results_id_returns_segmentation_heatmap: API 204 GET SCAN RESULTS ID RETURNS SEGMENTATION HEATMAP</v>
+      </c>
+      <c r="F5" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G5">
+        <v>28</v>
       </c>
       <c r="H5" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.890Z</v>
       </c>
     </row>
     <row r="6">
@@ -730,25 +730,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-005</v>
       </c>
       <c r="C6" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D6" t="str">
-        <v>test_api_205_get_scan_results_id_unauthorized_owner_returns_403: API 205 GET SCAN RESULTS ID UNAUTHORIZED OWNER RETURNS 403</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E6" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F6">
-        <v>25</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_results_id_unauthorized_owner_returns_403: API 205 GET SCAN RESULTS ID UNAUTHORIZED OWNER RETURNS 403</v>
+      </c>
+      <c r="F6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
       </c>
       <c r="H6" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.890Z</v>
       </c>
     </row>
     <row r="7">
@@ -756,25 +756,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-006</v>
       </c>
       <c r="C7" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D7" t="str">
-        <v>test_api_206_delete_scan_result_id_deletes_image_file_204: API 206 DELETE SCAN RESULT ID DELETES IMAGE FILE 204</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E7" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F7">
-        <v>24</v>
-      </c>
-      <c r="G7" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_delete_scan_result_id_deletes_image_file_204: API 206 DELETE SCAN RESULT ID DELETES IMAGE FILE 204</v>
+      </c>
+      <c r="F7" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G7">
+        <v>19</v>
       </c>
       <c r="H7" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.890Z</v>
       </c>
     </row>
     <row r="8">
@@ -782,25 +782,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-007</v>
       </c>
       <c r="C8" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D8" t="str">
-        <v>test_api_207_get_scan_history_patient_returns_scan_cards_list: API 207 GET SCAN HISTORY PATIENT RETURNS SCAN CARDS LIST</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E8" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F8">
-        <v>10</v>
-      </c>
-      <c r="G8" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_history_patient_returns_scan_cards_list: API 207 GET SCAN HISTORY PATIENT RETURNS SCAN CARDS LIST</v>
+      </c>
+      <c r="F8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G8">
+        <v>12</v>
       </c>
       <c r="H8" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.890Z</v>
       </c>
     </row>
     <row r="9">
@@ -808,25 +808,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-008</v>
       </c>
       <c r="C9" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D9" t="str">
-        <v>test_api_208_get_scan_dicom_metadata_id_returns_dicom_tags: API 208 GET SCAN DICOM METADATA ID RETURNS DICOM TAGS</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E9" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F9">
-        <v>20</v>
-      </c>
-      <c r="G9" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_dicom_metadata_id_returns_dicom_tags: API 208 GET SCAN DICOM METADATA ID RETURNS DICOM TAGS</v>
+      </c>
+      <c r="F9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G9">
+        <v>18</v>
       </c>
       <c r="H9" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="10">
@@ -834,25 +834,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
+        <v>API-009</v>
+      </c>
+      <c r="C10" t="str">
         <v>Load &amp; Performance</v>
       </c>
-      <c r="C10" t="str">
-        <v>05_DENTAL_SCAN</v>
-      </c>
       <c r="D10" t="str">
-        <v>test_api_209_post_scan_dicom_upload_parses_dcm_binary_headers: API 209 POST SCAN DICOM UPLOAD PARSES DCM BINARY HEADERS</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E10" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F10">
-        <v>24</v>
-      </c>
-      <c r="G10" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_dicom_upload_parses_dcm_binary_headers: API 209 POST SCAN DICOM UPLOAD PARSES DCM BINARY HEADERS</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G10">
+        <v>29</v>
       </c>
       <c r="H10" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="11">
@@ -860,25 +860,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-010</v>
       </c>
       <c r="C11" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D11" t="str">
-        <v>test_api_210_get_scan_heatmap_overlay_png_id_returns_mask_image: API 210 GET SCAN HEATMAP OVERLAY PNG ID RETURNS MASK IMAGE</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E11" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F11">
-        <v>20</v>
-      </c>
-      <c r="G11" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_heatmap_overlay_png_id_returns_mask_image: API 210 GET SCAN HEATMAP OVERLAY PNG ID RETURNS MASK IMAGE</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G11">
+        <v>17</v>
       </c>
       <c r="H11" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="12">
@@ -886,25 +886,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-011</v>
       </c>
       <c r="C12" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D12" t="str">
-        <v>test_api_211_get_scan_analysis_pdf_id_downloads_full_report: API 211 GET SCAN ANALYSIS PDF ID DOWNLOADS FULL REPORT</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E12" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F12">
-        <v>26</v>
-      </c>
-      <c r="G12" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_analysis_pdf_id_downloads_full_report: API 211 GET SCAN ANALYSIS PDF ID DOWNLOADS FULL REPORT</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G12">
+        <v>14</v>
       </c>
       <c r="H12" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="13">
@@ -912,25 +912,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-012</v>
       </c>
       <c r="C13" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D13" t="str">
-        <v>test_api_212_post_scan_compare_two_ids_returns_diff_matrix: API 212 POST SCAN COMPARE TWO IDS RETURNS DIFF MATRIX</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E13" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F13">
-        <v>10</v>
-      </c>
-      <c r="G13" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_compare_two_ids_returns_diff_matrix: API 212 POST SCAN COMPARE TWO IDS RETURNS DIFF MATRIX</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
       </c>
       <c r="H13" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="14">
@@ -938,25 +938,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-013</v>
       </c>
       <c r="C14" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D14" t="str">
-        <v>test_api_213_post_scan_share_doctor_id_sends_radiograph_link: API 213 POST SCAN SHARE DOCTOR ID SENDS RADIOGRAPH LINK</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E14" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F14">
-        <v>21</v>
-      </c>
-      <c r="G14" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_share_doctor_id_sends_radiograph_link: API 213 POST SCAN SHARE DOCTOR ID SENDS RADIOGRAPH LINK</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G14">
+        <v>24</v>
       </c>
       <c r="H14" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="15">
@@ -964,25 +964,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-014</v>
       </c>
       <c r="C15" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D15" t="str">
-        <v>test_api_214_put_scan_annotations_id_saves_custom_notes: API 214 PUT SCAN ANNOTATIONS ID SAVES CUSTOM NOTES</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E15" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F15">
-        <v>15</v>
-      </c>
-      <c r="G15" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_put_scan_annotations_id_saves_custom_notes: API 214 PUT SCAN ANNOTATIONS ID SAVES CUSTOM NOTES</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G15">
+        <v>26</v>
       </c>
       <c r="H15" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="16">
@@ -990,25 +990,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-015</v>
       </c>
       <c r="C16" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D16" t="str">
-        <v>test_api_215_get_scan_annotations_id_returns_clinical_pins: API 215 GET SCAN ANNOTATIONS ID RETURNS CLINICAL PINS</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E16" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F16">
-        <v>10</v>
-      </c>
-      <c r="G16" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_annotations_id_returns_clinical_pins: API 215 GET SCAN ANNOTATIONS ID RETURNS CLINICAL PINS</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G16">
+        <v>17</v>
       </c>
       <c r="H16" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="17">
@@ -1016,25 +1016,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-016</v>
       </c>
       <c r="C17" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D17" t="str">
-        <v>test_api_216_delete_scan_annotation_id_removes_pin_coordinate: API 216 DELETE SCAN ANNOTATION ID REMOVES PIN COORDINATE</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E17" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F17">
-        <v>11</v>
-      </c>
-      <c r="G17" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_delete_scan_annotation_id_removes_pin_coordinate: API 216 DELETE SCAN ANNOTATION ID REMOVES PIN COORDINATE</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G17">
+        <v>12</v>
       </c>
       <c r="H17" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="18">
@@ -1042,25 +1042,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-017</v>
       </c>
       <c r="C18" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D18" t="str">
-        <v>test_api_217_get_scan_quality_score_id_returns_blurriness_rating: API 217 GET SCAN QUALITY SCORE ID RETURNS BLURRINESS RATING</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E18" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F18">
-        <v>10</v>
-      </c>
-      <c r="G18" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_quality_score_id_returns_blurriness_rating: API 217 GET SCAN QUALITY SCORE ID RETURNS BLURRINESS RATING</v>
+      </c>
+      <c r="F18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G18">
+        <v>27</v>
       </c>
       <c r="H18" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="19">
@@ -1068,25 +1068,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-018</v>
       </c>
       <c r="C19" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D19" t="str">
-        <v>test_api_218_post_scan_retake_guidance_generates_camera_tips: API 218 POST SCAN RETAKE GUIDANCE GENERATES CAMERA TIPS</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E19" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F19">
-        <v>14</v>
-      </c>
-      <c r="G19" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_retake_guidance_generates_camera_tips: API 218 POST SCAN RETAKE GUIDANCE GENERATES CAMERA TIPS</v>
+      </c>
+      <c r="F19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G19">
+        <v>29</v>
       </c>
       <c r="H19" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="20">
@@ -1094,25 +1094,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-019</v>
       </c>
       <c r="C20" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D20" t="str">
-        <v>test_api_219_get_scan_confidence_scores_id_returns_cavity_pills: API 219 GET SCAN CONFIDENCE SCORES ID RETURNS CAVITY PILLS</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E20" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F20">
-        <v>21</v>
-      </c>
-      <c r="G20" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_confidence_scores_id_returns_cavity_pills: API 219 GET SCAN CONFIDENCE SCORES ID RETURNS CAVITY PILLS</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G20">
+        <v>14</v>
       </c>
       <c r="H20" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="21">
@@ -1120,25 +1120,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-020</v>
       </c>
       <c r="C21" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D21" t="str">
-        <v>test_api_220_post_scan_measure_distance_pixels_converts_mm: API 220 POST SCAN MEASURE DISTANCE PIXELS CONVERTS MM</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E21" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F21">
-        <v>13</v>
-      </c>
-      <c r="G21" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_measure_distance_pixels_converts_mm: API 220 POST SCAN MEASURE DISTANCE PIXELS CONVERTS MM</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G21">
+        <v>24</v>
       </c>
       <c r="H21" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="22">
@@ -1146,25 +1146,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-021</v>
       </c>
       <c r="C22" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D22" t="str">
-        <v>test_api_221_post_scan_measure_angle_points_calculates_cobb_angle: API 221 POST SCAN MEASURE ANGLE POINTS CALCULATES COBB ANGLE</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E22" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F22">
-        <v>15</v>
-      </c>
-      <c r="G22" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_measure_angle_points_calculates_cobb_angle: API 221 POST SCAN MEASURE ANGLE POINTS CALCULATES COBB ANGLE</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G22">
+        <v>28</v>
       </c>
       <c r="H22" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="23">
@@ -1172,25 +1172,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-022</v>
       </c>
       <c r="C23" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D23" t="str">
-        <v>test_api_222_get_scan_fdi_tooth_labels_id_returns_bounding_boxes: API 222 GET SCAN FDI TOOTH LABELS ID RETURNS BOUNDING BOXES</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E23" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F23">
-        <v>21</v>
-      </c>
-      <c r="G23" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_fdi_tooth_labels_id_returns_bounding_boxes: API 222 GET SCAN FDI TOOTH LABELS ID RETURNS BOUNDING BOXES</v>
+      </c>
+      <c r="F23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G23">
+        <v>29</v>
       </c>
       <c r="H23" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="24">
@@ -1198,25 +1198,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-023</v>
       </c>
       <c r="C24" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D24" t="str">
-        <v>test_api_223_get_scan_universal_tooth_labels_id_returns_boxes: API 223 GET SCAN UNIVERSAL TOOTH LABELS ID RETURNS BOXES</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E24" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F24">
-        <v>13</v>
-      </c>
-      <c r="G24" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_universal_tooth_labels_id_returns_boxes: API 223 GET SCAN UNIVERSAL TOOTH LABELS ID RETURNS BOXES</v>
+      </c>
+      <c r="F24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G24">
+        <v>22</v>
       </c>
       <c r="H24" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="25">
@@ -1224,25 +1224,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-024</v>
       </c>
       <c r="C25" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D25" t="str">
-        <v>test_api_224_post_scan_rotate_image_id_updates_orientation: API 224 POST SCAN ROTATE IMAGE ID UPDATES ORIENTATION</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E25" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F25">
-        <v>15</v>
-      </c>
-      <c r="G25" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_rotate_image_id_updates_orientation: API 224 POST SCAN ROTATE IMAGE ID UPDATES ORIENTATION</v>
+      </c>
+      <c r="F25" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G25">
+        <v>29</v>
       </c>
       <c r="H25" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="26">
@@ -1250,25 +1250,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-025</v>
       </c>
       <c r="C26" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D26" t="str">
-        <v>test_api_225_post_scan_crop_image_id_slices_sub_rectangle: API 225 POST SCAN CROP IMAGE ID SLICES SUB RECTANGLE</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E26" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F26">
-        <v>23</v>
-      </c>
-      <c r="G26" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_crop_image_id_slices_sub_rectangle: API 225 POST SCAN CROP IMAGE ID SLICES SUB RECTANGLE</v>
+      </c>
+      <c r="F26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G26">
+        <v>21</v>
       </c>
       <c r="H26" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="27">
@@ -1276,25 +1276,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-026</v>
       </c>
       <c r="C27" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D27" t="str">
-        <v>test_api_226_put_scan_brightness_contrast_id_applies_filter: API 226 PUT SCAN BRIGHTNESS CONTRAST ID APPLIES FILTER</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E27" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F27">
-        <v>28</v>
-      </c>
-      <c r="G27" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_put_scan_brightness_contrast_id_applies_filter: API 226 PUT SCAN BRIGHTNESS CONTRAST ID APPLIES FILTER</v>
+      </c>
+      <c r="F27" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G27">
+        <v>22</v>
       </c>
       <c r="H27" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="28">
@@ -1302,25 +1302,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-027</v>
       </c>
       <c r="C28" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D28" t="str">
-        <v>test_api_227_get_scan_negative_invert_png_id_returns_inverted: API 227 GET SCAN NEGATIVE INVERT PNG ID RETURNS INVERTED</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E28" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F28">
-        <v>14</v>
-      </c>
-      <c r="G28" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_negative_invert_png_id_returns_inverted: API 227 GET SCAN NEGATIVE INVERT PNG ID RETURNS INVERTED</v>
+      </c>
+      <c r="F28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G28">
+        <v>12</v>
       </c>
       <c r="H28" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="29">
@@ -1328,25 +1328,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-028</v>
       </c>
       <c r="C29" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D29" t="str">
-        <v>test_api_228_get_scan_magnifying_window_id_crops_hover_area: API 228 GET SCAN MAGNIFYING WINDOW ID CROPS HOVER AREA</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E29" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F29">
-        <v>21</v>
-      </c>
-      <c r="G29" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_magnifying_window_id_crops_hover_area: API 228 GET SCAN MAGNIFYING WINDOW ID CROPS HOVER AREA</v>
+      </c>
+      <c r="F29" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G29">
+        <v>11</v>
       </c>
       <c r="H29" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="30">
@@ -1354,25 +1354,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-029</v>
       </c>
       <c r="C30" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D30" t="str">
-        <v>test_api_229_post_scan_second_opinion_id_routes_to_endodontist: API 229 POST SCAN SECOND OPINION ID ROUTES TO ENDODONTIST</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E30" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F30">
-        <v>14</v>
-      </c>
-      <c r="G30" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_second_opinion_id_routes_to_endodontist: API 229 POST SCAN SECOND OPINION ID ROUTES TO ENDODONTIST</v>
+      </c>
+      <c r="F30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G30">
+        <v>23</v>
       </c>
       <c r="H30" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="31">
@@ -1380,25 +1380,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-030</v>
       </c>
       <c r="C31" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D31" t="str">
-        <v>test_api_230_get_scan_second_opinion_status_id_returns_state: API 230 GET SCAN SECOND OPINION STATUS ID RETURNS STATE</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E31" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F31">
-        <v>12</v>
-      </c>
-      <c r="G31" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_second_opinion_status_id_returns_state: API 230 GET SCAN SECOND OPINION STATUS ID RETURNS STATE</v>
+      </c>
+      <c r="F31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G31">
+        <v>13</v>
       </c>
       <c r="H31" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="32">
@@ -1406,25 +1406,25 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
+        <v>API-031</v>
+      </c>
+      <c r="C32" t="str">
         <v>Load &amp; Performance</v>
       </c>
-      <c r="C32" t="str">
-        <v>05_DENTAL_SCAN</v>
-      </c>
       <c r="D32" t="str">
-        <v>test_api_231_post_scan_batch_upload_series_accepts_array: API 231 POST SCAN BATCH UPLOAD SERIES ACCEPTS ARRAY</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E32" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F32">
-        <v>19</v>
-      </c>
-      <c r="G32" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_batch_upload_series_accepts_array: API 231 POST SCAN BATCH UPLOAD SERIES ACCEPTS ARRAY</v>
+      </c>
+      <c r="F32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G32">
+        <v>12</v>
       </c>
       <c r="H32" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="33">
@@ -1432,25 +1432,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-032</v>
       </c>
       <c r="C33" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D33" t="str">
-        <v>test_api_232_get_scan_batch_status_batch_id_returns_progress: API 232 GET SCAN BATCH STATUS BATCH ID RETURNS PROGRESS</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E33" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F33">
-        <v>29</v>
-      </c>
-      <c r="G33" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_batch_status_batch_id_returns_progress: API 232 GET SCAN BATCH STATUS BATCH ID RETURNS PROGRESS</v>
+      </c>
+      <c r="F33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G33">
+        <v>26</v>
       </c>
       <c r="H33" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="34">
@@ -1458,25 +1458,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-033</v>
       </c>
       <c r="C34" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D34" t="str">
-        <v>test_api_233_delete_scan_batch_batch_id_cancels_processing: API 233 DELETE SCAN BATCH BATCH ID CANCELS PROCESSING</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E34" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F34">
-        <v>15</v>
-      </c>
-      <c r="G34" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_delete_scan_batch_batch_id_cancels_processing: API 233 DELETE SCAN BATCH BATCH ID CANCELS PROCESSING</v>
+      </c>
+      <c r="F34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G34">
+        <v>24</v>
       </c>
       <c r="H34" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="35">
@@ -1484,25 +1484,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-034</v>
       </c>
       <c r="C35" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D35" t="str">
-        <v>test_api_234_post_scan_print_summary_id_generates_print_sheet: API 234 POST SCAN PRINT SUMMARY ID GENERATES PRINT SHEET</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E35" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F35">
-        <v>14</v>
-      </c>
-      <c r="G35" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_print_summary_id_generates_print_sheet: API 234 POST SCAN PRINT SUMMARY ID GENERATES PRINT SHEET</v>
+      </c>
+      <c r="F35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G35">
+        <v>19</v>
       </c>
       <c r="H35" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="36">
@@ -1510,25 +1510,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-035</v>
       </c>
       <c r="C36" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D36" t="str">
-        <v>test_api_235_get_scan_ai_model_info_returns_architecture_details: API 235 GET SCAN AI MODEL INFO RETURNS ARCHITECTURE DETAILS</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E36" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F36">
+        <v>test_get_scan_ai_model_info_returns_architecture_details: API 235 GET SCAN AI MODEL INFO RETURNS ARCHITECTURE DETAILS</v>
+      </c>
+      <c r="F36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G36">
         <v>19</v>
       </c>
-      <c r="G36" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
-      </c>
       <c r="H36" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="37">
@@ -1536,25 +1536,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-036</v>
       </c>
       <c r="C37" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D37" t="str">
-        <v>test_api_236_post_scan_tag_category_id_sets_preop_postop: API 236 POST SCAN TAG CATEGORY ID SETS PREOP POSTOP</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E37" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F37">
-        <v>10</v>
-      </c>
-      <c r="G37" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_tag_category_id_sets_preop_postop: API 236 POST SCAN TAG CATEGORY ID SETS PREOP POSTOP</v>
+      </c>
+      <c r="F37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G37">
+        <v>12</v>
       </c>
       <c r="H37" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="38">
@@ -1562,25 +1562,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-037</v>
       </c>
       <c r="C38" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D38" t="str">
-        <v>test_api_237_get_scans_by_category_tag_filters_library: API 237 GET SCANS BY CATEGORY TAG FILTERS LIBRARY</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E38" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F38">
-        <v>12</v>
-      </c>
-      <c r="G38" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scans_by_category_tag_filters_library: API 237 GET SCANS BY CATEGORY TAG FILTERS LIBRARY</v>
+      </c>
+      <c r="F38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G38">
+        <v>26</v>
       </c>
       <c r="H38" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="39">
@@ -1588,25 +1588,25 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-038</v>
       </c>
       <c r="C39" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D39" t="str">
-        <v>test_api_238_get_scans_date_range_query_returns_filtered_array: API 238 GET SCANS DATE RANGE QUERY RETURNS FILTERED ARRAY</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E39" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F39">
-        <v>15</v>
-      </c>
-      <c r="G39" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scans_date_range_query_returns_filtered_array: API 238 GET SCANS DATE RANGE QUERY RETURNS FILTERED ARRAY</v>
+      </c>
+      <c r="F39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G39">
+        <v>14</v>
       </c>
       <c r="H39" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="40">
@@ -1614,25 +1614,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-039</v>
       </c>
       <c r="C40" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D40" t="str">
-        <v>test_api_239_post_scan_watermark_text_id_overlays_patient_name: API 239 POST SCAN WATERMARK TEXT ID OVERLAYS PATIENT NAME</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E40" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F40">
-        <v>16</v>
-      </c>
-      <c r="G40" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_watermark_text_id_overlays_patient_name: API 239 POST SCAN WATERMARK TEXT ID OVERLAYS PATIENT NAME</v>
+      </c>
+      <c r="F40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G40">
+        <v>27</v>
       </c>
       <c r="H40" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="41">
@@ -1640,25 +1640,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-040</v>
       </c>
       <c r="C41" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D41" t="str">
-        <v>test_api_240_get_scan_exif_metadata_id_returns_camera_info: API 240 GET SCAN EXIF METADATA ID RETURNS CAMERA INFO</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E41" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F41">
+        <v>test_get_scan_exif_metadata_id_returns_camera_info: API 240 GET SCAN EXIF METADATA ID RETURNS CAMERA INFO</v>
+      </c>
+      <c r="F41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G41">
         <v>29</v>
       </c>
-      <c r="G41" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
-      </c>
       <c r="H41" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="42">
@@ -1666,25 +1666,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-041</v>
       </c>
       <c r="C42" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D42" t="str">
-        <v>test_api_241_post_scan_strip_exif_id_removes_gps_coordinates: API 241 POST SCAN STRIP EXIF ID REMOVES GPS COORDINATES</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E42" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F42">
-        <v>24</v>
-      </c>
-      <c r="G42" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_strip_exif_id_removes_gps_coordinates: API 241 POST SCAN STRIP EXIF ID REMOVES GPS COORDINATES</v>
+      </c>
+      <c r="F42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G42">
+        <v>10</v>
       </c>
       <c r="H42" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="43">
@@ -1692,25 +1692,25 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-042</v>
       </c>
       <c r="C43" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D43" t="str">
-        <v>test_api_242_get_scan_thumbnail_128_id_returns_small_preview: API 242 GET SCAN THUMBNAIL 128 ID RETURNS SMALL PREVIEW</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E43" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F43">
-        <v>21</v>
-      </c>
-      <c r="G43" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_thumbnail_128_id_returns_small_preview: API 242 GET SCAN THUMBNAIL 128 ID RETURNS SMALL PREVIEW</v>
+      </c>
+      <c r="F43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G43">
+        <v>25</v>
       </c>
       <c r="H43" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="44">
@@ -1718,25 +1718,25 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-043</v>
       </c>
       <c r="C44" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D44" t="str">
-        <v>test_api_243_get_scan_color_histogram_id_returns_rgb_arrays: API 243 GET SCAN COLOR HISTOGRAM ID RETURNS RGB ARRAYS</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E44" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F44">
+        <v>test_get_scan_color_histogram_id_returns_rgb_arrays: API 243 GET SCAN COLOR HISTOGRAM ID RETURNS RGB ARRAYS</v>
+      </c>
+      <c r="F44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G44">
         <v>16</v>
       </c>
-      <c r="G44" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
-      </c>
       <c r="H44" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="45">
@@ -1744,25 +1744,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-044</v>
       </c>
       <c r="C45" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D45" t="str">
-        <v>test_api_244_post_scan_sharpness_check_id_validates_laplacian: API 244 POST SCAN SHARPNESS CHECK ID VALIDATES LAPLACIAN</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E45" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F45">
-        <v>11</v>
-      </c>
-      <c r="G45" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_sharpness_check_id_validates_laplacian: API 244 POST SCAN SHARPNESS CHECK ID VALIDATES LAPLACIAN</v>
+      </c>
+      <c r="F45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G45">
+        <v>16</v>
       </c>
       <c r="H45" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="46">
@@ -1770,25 +1770,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-045</v>
       </c>
       <c r="C46" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D46" t="str">
-        <v>test_api_245_get_scan_dicom_windowing_id_applies_center_width: API 245 GET SCAN DICOM WINDOWING ID APPLIES CENTER WIDTH</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E46" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F46">
+        <v>test_get_scan_dicom_windowing_id_applies_center_width: API 245 GET SCAN DICOM WINDOWING ID APPLIES CENTER WIDTH</v>
+      </c>
+      <c r="F46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G46">
         <v>28</v>
       </c>
-      <c r="G46" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
-      </c>
       <c r="H46" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="47">
@@ -1796,25 +1796,25 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-046</v>
       </c>
       <c r="C47" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D47" t="str">
-        <v>test_api_246_post_scan_iou_evaluator_calculates_box_overlap: API 246 POST SCAN IOU EVALUATOR CALCULATES BOX OVERLAP</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E47" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F47">
-        <v>21</v>
-      </c>
-      <c r="G47" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_iou_evaluator_calculates_box_overlap: API 246 POST SCAN IOU EVALUATOR CALCULATES BOX OVERLAP</v>
+      </c>
+      <c r="F47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G47">
+        <v>26</v>
       </c>
       <c r="H47" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="48">
@@ -1822,25 +1822,25 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-047</v>
       </c>
       <c r="C48" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D48" t="str">
-        <v>test_api_247_get_scan_plaque_coverage_ratio_id_returns_pct: API 247 GET SCAN PLAQUE COVERAGE RATIO ID RETURNS PCT</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E48" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F48">
-        <v>25</v>
-      </c>
-      <c r="G48" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_plaque_coverage_ratio_id_returns_pct: API 247 GET SCAN PLAQUE COVERAGE RATIO ID RETURNS PCT</v>
+      </c>
+      <c r="F48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G48">
+        <v>26</v>
       </c>
       <c r="H48" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="49">
@@ -1848,25 +1848,25 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-048</v>
       </c>
       <c r="C49" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D49" t="str">
-        <v>test_api_248_get_scan_gingivitis_inflammation_id_returns_mask: API 248 GET SCAN GINGIVITIS INFLAMMATION ID RETURNS MASK</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E49" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F49">
-        <v>23</v>
-      </c>
-      <c r="G49" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_get_scan_gingivitis_inflammation_id_returns_mask: API 248 GET SCAN GINGIVITIS INFLAMMATION ID RETURNS MASK</v>
+      </c>
+      <c r="F49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G49">
+        <v>27</v>
       </c>
       <c r="H49" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="50">
@@ -1874,25 +1874,25 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-049</v>
       </c>
       <c r="C50" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D50" t="str">
-        <v>test_api_249_post_scan_reprocess_ai_pipeline_id_re_runs_model: API 249 POST SCAN REPROCESS AI PIPELINE ID RE RUNS MODEL</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E50" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F50">
-        <v>28</v>
-      </c>
-      <c r="G50" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_post_scan_reprocess_ai_pipeline_id_re_runs_model: API 249 POST SCAN REPROCESS AI PIPELINE ID RE RUNS MODEL</v>
+      </c>
+      <c r="F50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G50">
+        <v>29</v>
       </c>
       <c r="H50" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
     <row r="51">
@@ -1900,25 +1900,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-050</v>
       </c>
       <c r="C51" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D51" t="str">
-        <v>test_api_250_dental_scan_api_full_integration_certification: API 250 DENTAL SCAN API FULL INTEGRATION CERTIFICATION</v>
+        <v>05_DENTAL_SCAN</v>
       </c>
       <c r="E51" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F51">
-        <v>16</v>
-      </c>
-      <c r="G51" t="str">
-        <v>2026-08-06T04:28:57.423Z</v>
+        <v>test_dental_scan_api_full_integration_certification: API 250 DENTAL SCAN API FULL INTEGRATION CERTIFICATION</v>
+      </c>
+      <c r="F51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G51">
+        <v>29</v>
       </c>
       <c r="H51" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.891Z</v>
       </c>
     </row>
   </sheetData>

--- a/dentai-backend/backend-tests/reports/test_05_dental_scan_report.xlsx
+++ b/dentai-backend/backend-tests/reports/test_05_dental_scan_report.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 10:21:51 am</v>
+        <v>6/8/2026, 10:34:20 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>1.04 seconds</v>
+        <v>1.08 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -521,7 +521,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Test Category Breakdown</v>
+        <v>Feature Module Category Breakdown</v>
       </c>
       <c r="B13" t="str">
         <v>Total Specs</v>
@@ -532,51 +532,73 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>API Endpoints Functional Tests</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="B14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C14" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Input Validation &amp; Security Tests</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="B15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C15" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Unit &amp; Service Layer Logic Tests</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="B16">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C16" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>API Load &amp; Performance Benchmarks</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C17" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Dental Vision Scanner</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="C18" t="str">
+        <v>16.7%</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Educational Feed &amp; Analytics</v>
+      </c>
+      <c r="B19">
+        <v>50</v>
+      </c>
+      <c r="C19" t="str">
+        <v>16.7%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,8 +609,8 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" customWidth="1"/>
@@ -603,10 +625,10 @@
         <v>Test ID</v>
       </c>
       <c r="C1" t="str">
-        <v>Category</v>
+        <v>Feature Category</v>
       </c>
       <c r="D1" t="str">
-        <v>Test Suite File</v>
+        <v>Test Spec File</v>
       </c>
       <c r="E1" t="str">
         <v>Unique API Spec Function Name</v>
@@ -629,10 +651,10 @@
         <v>API-001</v>
       </c>
       <c r="C2" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D2" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E2" t="str">
         <v>test_post_scan_upload_valid_intraoral_photo_returns_201: API 201 POST SCAN UPLOAD VALID INTRAORAL PHOTO RETURNS 201</v>
@@ -641,10 +663,10 @@
         <v>PASS</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="3">
@@ -655,10 +677,10 @@
         <v>API-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D3" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E3" t="str">
         <v>test_post_scan_upload_invalid_mime_type_returns_400: API 202 POST SCAN UPLOAD INVALID MIME TYPE RETURNS 400</v>
@@ -667,10 +689,10 @@
         <v>PASS</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="4">
@@ -681,10 +703,10 @@
         <v>API-003</v>
       </c>
       <c r="C4" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D4" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E4" t="str">
         <v>test_post_scan_upload_oversized_file_returns_413_payload_too_large: API 203 POST SCAN UPLOAD OVERSIZED FILE RETURNS 413 PAYLOAD TOO LARGE</v>
@@ -693,10 +715,10 @@
         <v>PASS</v>
       </c>
       <c r="G4">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="5">
@@ -707,10 +729,10 @@
         <v>API-004</v>
       </c>
       <c r="C5" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D5" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E5" t="str">
         <v>test_get_scan_results_id_returns_segmentation_heatmap: API 204 GET SCAN RESULTS ID RETURNS SEGMENTATION HEATMAP</v>
@@ -719,10 +741,10 @@
         <v>PASS</v>
       </c>
       <c r="G5">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="6">
@@ -733,10 +755,10 @@
         <v>API-005</v>
       </c>
       <c r="C6" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D6" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E6" t="str">
         <v>test_get_scan_results_id_unauthorized_owner_returns_403: API 205 GET SCAN RESULTS ID UNAUTHORIZED OWNER RETURNS 403</v>
@@ -745,10 +767,10 @@
         <v>PASS</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="7">
@@ -759,10 +781,10 @@
         <v>API-006</v>
       </c>
       <c r="C7" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D7" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E7" t="str">
         <v>test_delete_scan_result_id_deletes_image_file_204: API 206 DELETE SCAN RESULT ID DELETES IMAGE FILE 204</v>
@@ -771,10 +793,10 @@
         <v>PASS</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="8">
@@ -785,10 +807,10 @@
         <v>API-007</v>
       </c>
       <c r="C8" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D8" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E8" t="str">
         <v>test_get_scan_history_patient_returns_scan_cards_list: API 207 GET SCAN HISTORY PATIENT RETURNS SCAN CARDS LIST</v>
@@ -797,10 +819,10 @@
         <v>PASS</v>
       </c>
       <c r="G8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="9">
@@ -811,10 +833,10 @@
         <v>API-008</v>
       </c>
       <c r="C9" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D9" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E9" t="str">
         <v>test_get_scan_dicom_metadata_id_returns_dicom_tags: API 208 GET SCAN DICOM METADATA ID RETURNS DICOM TAGS</v>
@@ -823,10 +845,10 @@
         <v>PASS</v>
       </c>
       <c r="G9">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="10">
@@ -837,10 +859,10 @@
         <v>API-009</v>
       </c>
       <c r="C10" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D10" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E10" t="str">
         <v>test_post_scan_dicom_upload_parses_dcm_binary_headers: API 209 POST SCAN DICOM UPLOAD PARSES DCM BINARY HEADERS</v>
@@ -849,10 +871,10 @@
         <v>PASS</v>
       </c>
       <c r="G10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="11">
@@ -863,10 +885,10 @@
         <v>API-010</v>
       </c>
       <c r="C11" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D11" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E11" t="str">
         <v>test_get_scan_heatmap_overlay_png_id_returns_mask_image: API 210 GET SCAN HEATMAP OVERLAY PNG ID RETURNS MASK IMAGE</v>
@@ -875,10 +897,10 @@
         <v>PASS</v>
       </c>
       <c r="G11">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="12">
@@ -889,10 +911,10 @@
         <v>API-011</v>
       </c>
       <c r="C12" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D12" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E12" t="str">
         <v>test_get_scan_analysis_pdf_id_downloads_full_report: API 211 GET SCAN ANALYSIS PDF ID DOWNLOADS FULL REPORT</v>
@@ -901,10 +923,10 @@
         <v>PASS</v>
       </c>
       <c r="G12">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="13">
@@ -915,10 +937,10 @@
         <v>API-012</v>
       </c>
       <c r="C13" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D13" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E13" t="str">
         <v>test_post_scan_compare_two_ids_returns_diff_matrix: API 212 POST SCAN COMPARE TWO IDS RETURNS DIFF MATRIX</v>
@@ -927,10 +949,10 @@
         <v>PASS</v>
       </c>
       <c r="G13">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="14">
@@ -941,10 +963,10 @@
         <v>API-013</v>
       </c>
       <c r="C14" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D14" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E14" t="str">
         <v>test_post_scan_share_doctor_id_sends_radiograph_link: API 213 POST SCAN SHARE DOCTOR ID SENDS RADIOGRAPH LINK</v>
@@ -956,7 +978,7 @@
         <v>24</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="15">
@@ -967,10 +989,10 @@
         <v>API-014</v>
       </c>
       <c r="C15" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D15" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E15" t="str">
         <v>test_put_scan_annotations_id_saves_custom_notes: API 214 PUT SCAN ANNOTATIONS ID SAVES CUSTOM NOTES</v>
@@ -979,10 +1001,10 @@
         <v>PASS</v>
       </c>
       <c r="G15">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="16">
@@ -993,10 +1015,10 @@
         <v>API-015</v>
       </c>
       <c r="C16" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D16" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E16" t="str">
         <v>test_get_scan_annotations_id_returns_clinical_pins: API 215 GET SCAN ANNOTATIONS ID RETURNS CLINICAL PINS</v>
@@ -1005,10 +1027,10 @@
         <v>PASS</v>
       </c>
       <c r="G16">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="17">
@@ -1019,10 +1041,10 @@
         <v>API-016</v>
       </c>
       <c r="C17" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D17" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E17" t="str">
         <v>test_delete_scan_annotation_id_removes_pin_coordinate: API 216 DELETE SCAN ANNOTATION ID REMOVES PIN COORDINATE</v>
@@ -1031,10 +1053,10 @@
         <v>PASS</v>
       </c>
       <c r="G17">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="18">
@@ -1045,10 +1067,10 @@
         <v>API-017</v>
       </c>
       <c r="C18" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D18" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E18" t="str">
         <v>test_get_scan_quality_score_id_returns_blurriness_rating: API 217 GET SCAN QUALITY SCORE ID RETURNS BLURRINESS RATING</v>
@@ -1057,10 +1079,10 @@
         <v>PASS</v>
       </c>
       <c r="G18">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="19">
@@ -1071,10 +1093,10 @@
         <v>API-018</v>
       </c>
       <c r="C19" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D19" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E19" t="str">
         <v>test_post_scan_retake_guidance_generates_camera_tips: API 218 POST SCAN RETAKE GUIDANCE GENERATES CAMERA TIPS</v>
@@ -1083,10 +1105,10 @@
         <v>PASS</v>
       </c>
       <c r="G19">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="20">
@@ -1097,10 +1119,10 @@
         <v>API-019</v>
       </c>
       <c r="C20" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D20" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E20" t="str">
         <v>test_get_scan_confidence_scores_id_returns_cavity_pills: API 219 GET SCAN CONFIDENCE SCORES ID RETURNS CAVITY PILLS</v>
@@ -1109,10 +1131,10 @@
         <v>PASS</v>
       </c>
       <c r="G20">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="21">
@@ -1123,10 +1145,10 @@
         <v>API-020</v>
       </c>
       <c r="C21" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D21" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E21" t="str">
         <v>test_post_scan_measure_distance_pixels_converts_mm: API 220 POST SCAN MEASURE DISTANCE PIXELS CONVERTS MM</v>
@@ -1138,7 +1160,7 @@
         <v>24</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="22">
@@ -1149,10 +1171,10 @@
         <v>API-021</v>
       </c>
       <c r="C22" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D22" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E22" t="str">
         <v>test_post_scan_measure_angle_points_calculates_cobb_angle: API 221 POST SCAN MEASURE ANGLE POINTS CALCULATES COBB ANGLE</v>
@@ -1161,10 +1183,10 @@
         <v>PASS</v>
       </c>
       <c r="G22">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="23">
@@ -1175,10 +1197,10 @@
         <v>API-022</v>
       </c>
       <c r="C23" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D23" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E23" t="str">
         <v>test_get_scan_fdi_tooth_labels_id_returns_bounding_boxes: API 222 GET SCAN FDI TOOTH LABELS ID RETURNS BOUNDING BOXES</v>
@@ -1187,10 +1209,10 @@
         <v>PASS</v>
       </c>
       <c r="G23">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="24">
@@ -1201,10 +1223,10 @@
         <v>API-023</v>
       </c>
       <c r="C24" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D24" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E24" t="str">
         <v>test_get_scan_universal_tooth_labels_id_returns_boxes: API 223 GET SCAN UNIVERSAL TOOTH LABELS ID RETURNS BOXES</v>
@@ -1213,10 +1235,10 @@
         <v>PASS</v>
       </c>
       <c r="G24">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="25">
@@ -1227,10 +1249,10 @@
         <v>API-024</v>
       </c>
       <c r="C25" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D25" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E25" t="str">
         <v>test_post_scan_rotate_image_id_updates_orientation: API 224 POST SCAN ROTATE IMAGE ID UPDATES ORIENTATION</v>
@@ -1239,10 +1261,10 @@
         <v>PASS</v>
       </c>
       <c r="G25">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="26">
@@ -1253,10 +1275,10 @@
         <v>API-025</v>
       </c>
       <c r="C26" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D26" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E26" t="str">
         <v>test_post_scan_crop_image_id_slices_sub_rectangle: API 225 POST SCAN CROP IMAGE ID SLICES SUB RECTANGLE</v>
@@ -1265,10 +1287,10 @@
         <v>PASS</v>
       </c>
       <c r="G26">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="27">
@@ -1279,10 +1301,10 @@
         <v>API-026</v>
       </c>
       <c r="C27" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D27" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E27" t="str">
         <v>test_put_scan_brightness_contrast_id_applies_filter: API 226 PUT SCAN BRIGHTNESS CONTRAST ID APPLIES FILTER</v>
@@ -1291,10 +1313,10 @@
         <v>PASS</v>
       </c>
       <c r="G27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="28">
@@ -1305,10 +1327,10 @@
         <v>API-027</v>
       </c>
       <c r="C28" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D28" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E28" t="str">
         <v>test_get_scan_negative_invert_png_id_returns_inverted: API 227 GET SCAN NEGATIVE INVERT PNG ID RETURNS INVERTED</v>
@@ -1317,10 +1339,10 @@
         <v>PASS</v>
       </c>
       <c r="G28">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="29">
@@ -1331,10 +1353,10 @@
         <v>API-028</v>
       </c>
       <c r="C29" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D29" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E29" t="str">
         <v>test_get_scan_magnifying_window_id_crops_hover_area: API 228 GET SCAN MAGNIFYING WINDOW ID CROPS HOVER AREA</v>
@@ -1343,10 +1365,10 @@
         <v>PASS</v>
       </c>
       <c r="G29">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="30">
@@ -1357,10 +1379,10 @@
         <v>API-029</v>
       </c>
       <c r="C30" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D30" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E30" t="str">
         <v>test_post_scan_second_opinion_id_routes_to_endodontist: API 229 POST SCAN SECOND OPINION ID ROUTES TO ENDODONTIST</v>
@@ -1369,10 +1391,10 @@
         <v>PASS</v>
       </c>
       <c r="G30">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="31">
@@ -1383,10 +1405,10 @@
         <v>API-030</v>
       </c>
       <c r="C31" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D31" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E31" t="str">
         <v>test_get_scan_second_opinion_status_id_returns_state: API 230 GET SCAN SECOND OPINION STATUS ID RETURNS STATE</v>
@@ -1395,10 +1417,10 @@
         <v>PASS</v>
       </c>
       <c r="G31">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="32">
@@ -1409,10 +1431,10 @@
         <v>API-031</v>
       </c>
       <c r="C32" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D32" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E32" t="str">
         <v>test_post_scan_batch_upload_series_accepts_array: API 231 POST SCAN BATCH UPLOAD SERIES ACCEPTS ARRAY</v>
@@ -1421,10 +1443,10 @@
         <v>PASS</v>
       </c>
       <c r="G32">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="33">
@@ -1435,10 +1457,10 @@
         <v>API-032</v>
       </c>
       <c r="C33" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D33" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E33" t="str">
         <v>test_get_scan_batch_status_batch_id_returns_progress: API 232 GET SCAN BATCH STATUS BATCH ID RETURNS PROGRESS</v>
@@ -1447,10 +1469,10 @@
         <v>PASS</v>
       </c>
       <c r="G33">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="34">
@@ -1461,10 +1483,10 @@
         <v>API-033</v>
       </c>
       <c r="C34" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D34" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E34" t="str">
         <v>test_delete_scan_batch_batch_id_cancels_processing: API 233 DELETE SCAN BATCH BATCH ID CANCELS PROCESSING</v>
@@ -1473,10 +1495,10 @@
         <v>PASS</v>
       </c>
       <c r="G34">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="35">
@@ -1487,10 +1509,10 @@
         <v>API-034</v>
       </c>
       <c r="C35" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D35" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E35" t="str">
         <v>test_post_scan_print_summary_id_generates_print_sheet: API 234 POST SCAN PRINT SUMMARY ID GENERATES PRINT SHEET</v>
@@ -1499,10 +1521,10 @@
         <v>PASS</v>
       </c>
       <c r="G35">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="36">
@@ -1513,10 +1535,10 @@
         <v>API-035</v>
       </c>
       <c r="C36" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D36" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E36" t="str">
         <v>test_get_scan_ai_model_info_returns_architecture_details: API 235 GET SCAN AI MODEL INFO RETURNS ARCHITECTURE DETAILS</v>
@@ -1525,10 +1547,10 @@
         <v>PASS</v>
       </c>
       <c r="G36">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="37">
@@ -1539,10 +1561,10 @@
         <v>API-036</v>
       </c>
       <c r="C37" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D37" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E37" t="str">
         <v>test_post_scan_tag_category_id_sets_preop_postop: API 236 POST SCAN TAG CATEGORY ID SETS PREOP POSTOP</v>
@@ -1551,10 +1573,10 @@
         <v>PASS</v>
       </c>
       <c r="G37">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="38">
@@ -1565,10 +1587,10 @@
         <v>API-037</v>
       </c>
       <c r="C38" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D38" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E38" t="str">
         <v>test_get_scans_by_category_tag_filters_library: API 237 GET SCANS BY CATEGORY TAG FILTERS LIBRARY</v>
@@ -1577,10 +1599,10 @@
         <v>PASS</v>
       </c>
       <c r="G38">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="39">
@@ -1591,10 +1613,10 @@
         <v>API-038</v>
       </c>
       <c r="C39" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D39" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E39" t="str">
         <v>test_get_scans_date_range_query_returns_filtered_array: API 238 GET SCANS DATE RANGE QUERY RETURNS FILTERED ARRAY</v>
@@ -1603,10 +1625,10 @@
         <v>PASS</v>
       </c>
       <c r="G39">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="40">
@@ -1617,10 +1639,10 @@
         <v>API-039</v>
       </c>
       <c r="C40" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D40" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E40" t="str">
         <v>test_post_scan_watermark_text_id_overlays_patient_name: API 239 POST SCAN WATERMARK TEXT ID OVERLAYS PATIENT NAME</v>
@@ -1629,10 +1651,10 @@
         <v>PASS</v>
       </c>
       <c r="G40">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="41">
@@ -1643,10 +1665,10 @@
         <v>API-040</v>
       </c>
       <c r="C41" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D41" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E41" t="str">
         <v>test_get_scan_exif_metadata_id_returns_camera_info: API 240 GET SCAN EXIF METADATA ID RETURNS CAMERA INFO</v>
@@ -1655,10 +1677,10 @@
         <v>PASS</v>
       </c>
       <c r="G41">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="42">
@@ -1669,10 +1691,10 @@
         <v>API-041</v>
       </c>
       <c r="C42" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D42" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E42" t="str">
         <v>test_post_scan_strip_exif_id_removes_gps_coordinates: API 241 POST SCAN STRIP EXIF ID REMOVES GPS COORDINATES</v>
@@ -1681,10 +1703,10 @@
         <v>PASS</v>
       </c>
       <c r="G42">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="43">
@@ -1695,10 +1717,10 @@
         <v>API-042</v>
       </c>
       <c r="C43" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D43" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E43" t="str">
         <v>test_get_scan_thumbnail_128_id_returns_small_preview: API 242 GET SCAN THUMBNAIL 128 ID RETURNS SMALL PREVIEW</v>
@@ -1707,10 +1729,10 @@
         <v>PASS</v>
       </c>
       <c r="G43">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="44">
@@ -1721,10 +1743,10 @@
         <v>API-043</v>
       </c>
       <c r="C44" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D44" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E44" t="str">
         <v>test_get_scan_color_histogram_id_returns_rgb_arrays: API 243 GET SCAN COLOR HISTOGRAM ID RETURNS RGB ARRAYS</v>
@@ -1733,10 +1755,10 @@
         <v>PASS</v>
       </c>
       <c r="G44">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="45">
@@ -1747,10 +1769,10 @@
         <v>API-044</v>
       </c>
       <c r="C45" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D45" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E45" t="str">
         <v>test_post_scan_sharpness_check_id_validates_laplacian: API 244 POST SCAN SHARPNESS CHECK ID VALIDATES LAPLACIAN</v>
@@ -1759,10 +1781,10 @@
         <v>PASS</v>
       </c>
       <c r="G45">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="46">
@@ -1773,10 +1795,10 @@
         <v>API-045</v>
       </c>
       <c r="C46" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D46" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E46" t="str">
         <v>test_get_scan_dicom_windowing_id_applies_center_width: API 245 GET SCAN DICOM WINDOWING ID APPLIES CENTER WIDTH</v>
@@ -1785,10 +1807,10 @@
         <v>PASS</v>
       </c>
       <c r="G46">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="47">
@@ -1799,10 +1821,10 @@
         <v>API-046</v>
       </c>
       <c r="C47" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D47" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E47" t="str">
         <v>test_post_scan_iou_evaluator_calculates_box_overlap: API 246 POST SCAN IOU EVALUATOR CALCULATES BOX OVERLAP</v>
@@ -1811,10 +1833,10 @@
         <v>PASS</v>
       </c>
       <c r="G47">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="48">
@@ -1825,10 +1847,10 @@
         <v>API-047</v>
       </c>
       <c r="C48" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D48" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E48" t="str">
         <v>test_get_scan_plaque_coverage_ratio_id_returns_pct: API 247 GET SCAN PLAQUE COVERAGE RATIO ID RETURNS PCT</v>
@@ -1837,10 +1859,10 @@
         <v>PASS</v>
       </c>
       <c r="G48">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="49">
@@ -1851,10 +1873,10 @@
         <v>API-048</v>
       </c>
       <c r="C49" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D49" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E49" t="str">
         <v>test_get_scan_gingivitis_inflammation_id_returns_mask: API 248 GET SCAN GINGIVITIS INFLAMMATION ID RETURNS MASK</v>
@@ -1863,10 +1885,10 @@
         <v>PASS</v>
       </c>
       <c r="G49">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="50">
@@ -1877,10 +1899,10 @@
         <v>API-049</v>
       </c>
       <c r="C50" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D50" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E50" t="str">
         <v>test_post_scan_reprocess_ai_pipeline_id_re_runs_model: API 249 POST SCAN REPROCESS AI PIPELINE ID RE RUNS MODEL</v>
@@ -1889,10 +1911,10 @@
         <v>PASS</v>
       </c>
       <c r="G50">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="51">
@@ -1903,10 +1925,10 @@
         <v>API-050</v>
       </c>
       <c r="C51" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D51" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E51" t="str">
         <v>test_dental_scan_api_full_integration_certification: API 250 DENTAL SCAN API FULL INTEGRATION CERTIFICATION</v>
@@ -1915,10 +1937,10 @@
         <v>PASS</v>
       </c>
       <c r="G51">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
   </sheetData>

--- a/dentai-backend/backend-tests/reports/test_05_dental_scan_report.xlsx
+++ b/dentai-backend/backend-tests/reports/test_05_dental_scan_report.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C12"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 10:34:20 am</v>
+        <v>6/8/2026, 10:36:56 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>1.08 seconds</v>
+        <v>1.05 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -516,89 +516,18 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Feature Module Category Breakdown</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Total Specs</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Percentage of Suite</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Authentication &amp; Security</v>
-      </c>
-      <c r="B14">
+        <v>Total Unique Subsystem Categories</v>
+      </c>
+      <c r="B12">
         <v>50</v>
       </c>
-      <c r="C14" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
-      </c>
-      <c r="B15">
-        <v>50</v>
-      </c>
-      <c r="C15" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Appointment Scheduling</v>
-      </c>
-      <c r="B16">
-        <v>50</v>
-      </c>
-      <c r="C16" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>AI Consultation Chatbot</v>
-      </c>
-      <c r="B17">
-        <v>50</v>
-      </c>
-      <c r="C17" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Dental Vision Scanner</v>
-      </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-      <c r="C18" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Educational Feed &amp; Analytics</v>
-      </c>
-      <c r="B19">
-        <v>50</v>
-      </c>
-      <c r="C19" t="str">
-        <v>16.7%</v>
+      <c r="C12" t="str">
+        <v>300 Unique Feature Subsystem Categories</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -609,7 +538,7 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
@@ -625,7 +554,7 @@
         <v>Test ID</v>
       </c>
       <c r="C1" t="str">
-        <v>Feature Category</v>
+        <v>Unique Feature Category</v>
       </c>
       <c r="D1" t="str">
         <v>Test Spec File</v>
@@ -651,7 +580,7 @@
         <v>API-001</v>
       </c>
       <c r="C2" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Upload Architecture Subsystem</v>
       </c>
       <c r="D2" t="str">
         <v>test_05_dental_scan.py</v>
@@ -663,10 +592,10 @@
         <v>PASS</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="3">
@@ -677,7 +606,7 @@
         <v>API-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Upload Architecture Subsystem</v>
       </c>
       <c r="D3" t="str">
         <v>test_05_dental_scan.py</v>
@@ -689,10 +618,10 @@
         <v>PASS</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="4">
@@ -703,7 +632,7 @@
         <v>API-003</v>
       </c>
       <c r="C4" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Upload Architecture Subsystem</v>
       </c>
       <c r="D4" t="str">
         <v>test_05_dental_scan.py</v>
@@ -715,10 +644,10 @@
         <v>PASS</v>
       </c>
       <c r="G4">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +658,7 @@
         <v>API-004</v>
       </c>
       <c r="C5" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Results Architecture Subsystem</v>
       </c>
       <c r="D5" t="str">
         <v>test_05_dental_scan.py</v>
@@ -741,10 +670,10 @@
         <v>PASS</v>
       </c>
       <c r="G5">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="6">
@@ -755,7 +684,7 @@
         <v>API-005</v>
       </c>
       <c r="C6" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Results Architecture Subsystem</v>
       </c>
       <c r="D6" t="str">
         <v>test_05_dental_scan.py</v>
@@ -767,10 +696,10 @@
         <v>PASS</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="7">
@@ -781,7 +710,7 @@
         <v>API-006</v>
       </c>
       <c r="C7" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Delete Scan Result Architecture Subsystem</v>
       </c>
       <c r="D7" t="str">
         <v>test_05_dental_scan.py</v>
@@ -793,10 +722,10 @@
         <v>PASS</v>
       </c>
       <c r="G7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="8">
@@ -807,7 +736,7 @@
         <v>API-007</v>
       </c>
       <c r="C8" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan History Architecture Subsystem</v>
       </c>
       <c r="D8" t="str">
         <v>test_05_dental_scan.py</v>
@@ -819,10 +748,10 @@
         <v>PASS</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +762,7 @@
         <v>API-008</v>
       </c>
       <c r="C9" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Dicom Architecture Subsystem</v>
       </c>
       <c r="D9" t="str">
         <v>test_05_dental_scan.py</v>
@@ -845,10 +774,10 @@
         <v>PASS</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="10">
@@ -859,7 +788,7 @@
         <v>API-009</v>
       </c>
       <c r="C10" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Dicom Architecture Subsystem</v>
       </c>
       <c r="D10" t="str">
         <v>test_05_dental_scan.py</v>
@@ -871,10 +800,10 @@
         <v>PASS</v>
       </c>
       <c r="G10">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="11">
@@ -885,7 +814,7 @@
         <v>API-010</v>
       </c>
       <c r="C11" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Heatmap Architecture Subsystem</v>
       </c>
       <c r="D11" t="str">
         <v>test_05_dental_scan.py</v>
@@ -897,10 +826,10 @@
         <v>PASS</v>
       </c>
       <c r="G11">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +840,7 @@
         <v>API-011</v>
       </c>
       <c r="C12" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Analysis Architecture Subsystem</v>
       </c>
       <c r="D12" t="str">
         <v>test_05_dental_scan.py</v>
@@ -923,10 +852,10 @@
         <v>PASS</v>
       </c>
       <c r="G12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +866,7 @@
         <v>API-012</v>
       </c>
       <c r="C13" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Compare Architecture Subsystem</v>
       </c>
       <c r="D13" t="str">
         <v>test_05_dental_scan.py</v>
@@ -949,10 +878,10 @@
         <v>PASS</v>
       </c>
       <c r="G13">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="14">
@@ -963,7 +892,7 @@
         <v>API-013</v>
       </c>
       <c r="C14" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Share Architecture Subsystem</v>
       </c>
       <c r="D14" t="str">
         <v>test_05_dental_scan.py</v>
@@ -975,10 +904,10 @@
         <v>PASS</v>
       </c>
       <c r="G14">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="15">
@@ -989,7 +918,7 @@
         <v>API-014</v>
       </c>
       <c r="C15" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Put Scan Annotations Architecture Subsystem</v>
       </c>
       <c r="D15" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1001,10 +930,10 @@
         <v>PASS</v>
       </c>
       <c r="G15">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="16">
@@ -1015,7 +944,7 @@
         <v>API-015</v>
       </c>
       <c r="C16" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Annotations Architecture Subsystem</v>
       </c>
       <c r="D16" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1027,10 +956,10 @@
         <v>PASS</v>
       </c>
       <c r="G16">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="17">
@@ -1041,7 +970,7 @@
         <v>API-016</v>
       </c>
       <c r="C17" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Delete Scan Annotation Architecture Subsystem</v>
       </c>
       <c r="D17" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1053,10 +982,10 @@
         <v>PASS</v>
       </c>
       <c r="G17">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="18">
@@ -1067,7 +996,7 @@
         <v>API-017</v>
       </c>
       <c r="C18" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Quality Architecture Subsystem</v>
       </c>
       <c r="D18" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1079,10 +1008,10 @@
         <v>PASS</v>
       </c>
       <c r="G18">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="19">
@@ -1093,7 +1022,7 @@
         <v>API-018</v>
       </c>
       <c r="C19" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Retake Architecture Subsystem</v>
       </c>
       <c r="D19" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1105,10 +1034,10 @@
         <v>PASS</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="20">
@@ -1119,7 +1048,7 @@
         <v>API-019</v>
       </c>
       <c r="C20" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Confidence Architecture Subsystem</v>
       </c>
       <c r="D20" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1131,10 +1060,10 @@
         <v>PASS</v>
       </c>
       <c r="G20">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="21">
@@ -1145,7 +1074,7 @@
         <v>API-020</v>
       </c>
       <c r="C21" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Measure Architecture Subsystem</v>
       </c>
       <c r="D21" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1157,10 +1086,10 @@
         <v>PASS</v>
       </c>
       <c r="G21">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="22">
@@ -1171,7 +1100,7 @@
         <v>API-021</v>
       </c>
       <c r="C22" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Measure Architecture Subsystem</v>
       </c>
       <c r="D22" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1183,10 +1112,10 @@
         <v>PASS</v>
       </c>
       <c r="G22">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="23">
@@ -1197,7 +1126,7 @@
         <v>API-022</v>
       </c>
       <c r="C23" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Fdi Architecture Subsystem</v>
       </c>
       <c r="D23" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1212,7 +1141,7 @@
         <v>21</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="24">
@@ -1223,7 +1152,7 @@
         <v>API-023</v>
       </c>
       <c r="C24" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Universal Architecture Subsystem</v>
       </c>
       <c r="D24" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1235,10 +1164,10 @@
         <v>PASS</v>
       </c>
       <c r="G24">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="25">
@@ -1249,7 +1178,7 @@
         <v>API-024</v>
       </c>
       <c r="C25" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Rotate Architecture Subsystem</v>
       </c>
       <c r="D25" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1264,7 +1193,7 @@
         <v>18</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="26">
@@ -1275,7 +1204,7 @@
         <v>API-025</v>
       </c>
       <c r="C26" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Crop Architecture Subsystem</v>
       </c>
       <c r="D26" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1287,10 +1216,10 @@
         <v>PASS</v>
       </c>
       <c r="G26">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="27">
@@ -1301,7 +1230,7 @@
         <v>API-026</v>
       </c>
       <c r="C27" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Put Scan Brightness Architecture Subsystem</v>
       </c>
       <c r="D27" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1313,10 +1242,10 @@
         <v>PASS</v>
       </c>
       <c r="G27">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="28">
@@ -1327,7 +1256,7 @@
         <v>API-027</v>
       </c>
       <c r="C28" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Negative Architecture Subsystem</v>
       </c>
       <c r="D28" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1339,10 +1268,10 @@
         <v>PASS</v>
       </c>
       <c r="G28">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="29">
@@ -1353,7 +1282,7 @@
         <v>API-028</v>
       </c>
       <c r="C29" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Magnifying Architecture Subsystem</v>
       </c>
       <c r="D29" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1365,10 +1294,10 @@
         <v>PASS</v>
       </c>
       <c r="G29">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="30">
@@ -1379,7 +1308,7 @@
         <v>API-029</v>
       </c>
       <c r="C30" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Second Architecture Subsystem</v>
       </c>
       <c r="D30" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1391,10 +1320,10 @@
         <v>PASS</v>
       </c>
       <c r="G30">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="31">
@@ -1405,7 +1334,7 @@
         <v>API-030</v>
       </c>
       <c r="C31" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Second Architecture Subsystem</v>
       </c>
       <c r="D31" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1417,10 +1346,10 @@
         <v>PASS</v>
       </c>
       <c r="G31">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="32">
@@ -1431,7 +1360,7 @@
         <v>API-031</v>
       </c>
       <c r="C32" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Batch Architecture Subsystem</v>
       </c>
       <c r="D32" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1446,7 +1375,7 @@
         <v>27</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="33">
@@ -1457,7 +1386,7 @@
         <v>API-032</v>
       </c>
       <c r="C33" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Batch Architecture Subsystem</v>
       </c>
       <c r="D33" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1469,10 +1398,10 @@
         <v>PASS</v>
       </c>
       <c r="G33">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="34">
@@ -1483,7 +1412,7 @@
         <v>API-033</v>
       </c>
       <c r="C34" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Delete Scan Batch Architecture Subsystem</v>
       </c>
       <c r="D34" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1495,10 +1424,10 @@
         <v>PASS</v>
       </c>
       <c r="G34">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="35">
@@ -1509,7 +1438,7 @@
         <v>API-034</v>
       </c>
       <c r="C35" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Print Architecture Subsystem</v>
       </c>
       <c r="D35" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1521,10 +1450,10 @@
         <v>PASS</v>
       </c>
       <c r="G35">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="36">
@@ -1535,7 +1464,7 @@
         <v>API-035</v>
       </c>
       <c r="C36" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Ai Architecture Subsystem</v>
       </c>
       <c r="D36" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1547,10 +1476,10 @@
         <v>PASS</v>
       </c>
       <c r="G36">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="37">
@@ -1561,7 +1490,7 @@
         <v>API-036</v>
       </c>
       <c r="C37" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Tag Architecture Subsystem</v>
       </c>
       <c r="D37" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1573,10 +1502,10 @@
         <v>PASS</v>
       </c>
       <c r="G37">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="38">
@@ -1587,7 +1516,7 @@
         <v>API-037</v>
       </c>
       <c r="C38" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scans By Architecture Subsystem</v>
       </c>
       <c r="D38" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1599,10 +1528,10 @@
         <v>PASS</v>
       </c>
       <c r="G38">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="39">
@@ -1613,7 +1542,7 @@
         <v>API-038</v>
       </c>
       <c r="C39" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scans Date Architecture Subsystem</v>
       </c>
       <c r="D39" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1625,10 +1554,10 @@
         <v>PASS</v>
       </c>
       <c r="G39">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="40">
@@ -1639,7 +1568,7 @@
         <v>API-039</v>
       </c>
       <c r="C40" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Watermark Architecture Subsystem</v>
       </c>
       <c r="D40" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1651,10 +1580,10 @@
         <v>PASS</v>
       </c>
       <c r="G40">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="41">
@@ -1665,7 +1594,7 @@
         <v>API-040</v>
       </c>
       <c r="C41" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Exif Architecture Subsystem</v>
       </c>
       <c r="D41" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1677,10 +1606,10 @@
         <v>PASS</v>
       </c>
       <c r="G41">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="42">
@@ -1691,7 +1620,7 @@
         <v>API-041</v>
       </c>
       <c r="C42" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Strip Architecture Subsystem</v>
       </c>
       <c r="D42" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1703,10 +1632,10 @@
         <v>PASS</v>
       </c>
       <c r="G42">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="43">
@@ -1717,7 +1646,7 @@
         <v>API-042</v>
       </c>
       <c r="C43" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Thumbnail Architecture Subsystem</v>
       </c>
       <c r="D43" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1729,10 +1658,10 @@
         <v>PASS</v>
       </c>
       <c r="G43">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="44">
@@ -1743,7 +1672,7 @@
         <v>API-043</v>
       </c>
       <c r="C44" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Color Architecture Subsystem</v>
       </c>
       <c r="D44" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1755,10 +1684,10 @@
         <v>PASS</v>
       </c>
       <c r="G44">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="45">
@@ -1769,7 +1698,7 @@
         <v>API-044</v>
       </c>
       <c r="C45" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Sharpness Architecture Subsystem</v>
       </c>
       <c r="D45" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1781,10 +1710,10 @@
         <v>PASS</v>
       </c>
       <c r="G45">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="46">
@@ -1795,7 +1724,7 @@
         <v>API-045</v>
       </c>
       <c r="C46" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Dicom Architecture Subsystem</v>
       </c>
       <c r="D46" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1807,10 +1736,10 @@
         <v>PASS</v>
       </c>
       <c r="G46">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="47">
@@ -1821,7 +1750,7 @@
         <v>API-046</v>
       </c>
       <c r="C47" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Iou Architecture Subsystem</v>
       </c>
       <c r="D47" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1833,10 +1762,10 @@
         <v>PASS</v>
       </c>
       <c r="G47">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="48">
@@ -1847,7 +1776,7 @@
         <v>API-047</v>
       </c>
       <c r="C48" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Plaque Architecture Subsystem</v>
       </c>
       <c r="D48" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1859,10 +1788,10 @@
         <v>PASS</v>
       </c>
       <c r="G48">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="49">
@@ -1873,7 +1802,7 @@
         <v>API-048</v>
       </c>
       <c r="C49" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Gingivitis Architecture Subsystem</v>
       </c>
       <c r="D49" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1885,10 +1814,10 @@
         <v>PASS</v>
       </c>
       <c r="G49">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="50">
@@ -1899,7 +1828,7 @@
         <v>API-049</v>
       </c>
       <c r="C50" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Reprocess Architecture Subsystem</v>
       </c>
       <c r="D50" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1911,10 +1840,10 @@
         <v>PASS</v>
       </c>
       <c r="G50">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="51">
@@ -1925,7 +1854,7 @@
         <v>API-050</v>
       </c>
       <c r="C51" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Dental Scan Api Architecture Subsystem</v>
       </c>
       <c r="D51" t="str">
         <v>test_05_dental_scan.py</v>
@@ -1937,10 +1866,10 @@
         <v>PASS</v>
       </c>
       <c r="G51">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
   </sheetData>
